--- a/output/pdf_financials_xlsx/PINK.xlsx
+++ b/output/pdf_financials_xlsx/PINK.xlsx
@@ -1375,16 +1375,16 @@
         <v>7.873731</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>3.723132</v>
+        <v>28.439048</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>13.980176</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.184046</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.471578</v>
       </c>
     </row>
     <row r="35">
@@ -1431,16 +1431,16 @@
         <v>7.873731</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3.723132</v>
+        <v>28.439048</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>13.980176</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.184046</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.471578</v>
       </c>
     </row>
     <row r="37">
@@ -1767,16 +1767,16 @@
         <v>1.976292</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>25.752988</v>
+        <v>1.037072</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>15.101545</v>
+        <v>1.121369</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.415687</v>
+        <v>1.231641</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.969064</v>
+        <v>0.497486</v>
       </c>
     </row>
     <row r="49">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/output/pdf_financials_xlsx/PINK.xlsx
+++ b/output/pdf_financials_xlsx/PINK.xlsx
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.036778</v>
+        <v>0.135683</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.122941</v>
+        <v>0.21304</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -22706,7 +22706,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E371" s="5" t="n">
         <v>0.09890500000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/PINK.xlsx
+++ b/output/pdf_financials_xlsx/PINK.xlsx
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.046947</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-1.67123</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-1.991369</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>-0.474503</v>
@@ -4181,16 +4181,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.046947</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-1.67123</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-1.991369</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>-0.474503</v>
@@ -4209,16 +4209,16 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-5.785153</v>
+        <v>-5.8321</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-8.262987000000001</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-10.923634</v>
+        <v>-12.594864</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-11.867905</v>
+        <v>-13.859274</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-15.170756</v>
@@ -12199,7 +12199,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="n">
         <v>-0.046947</v>
       </c>
@@ -12591,7 +12595,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -13895,7 +13903,11 @@
           <t>Purchase of equipment 8</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -14803,7 +14815,11 @@
           <t>Net proceeds from private placement 13</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E214" s="5" t="n">
         <v>4.082355</v>
       </c>
